--- a/tables/tables performance/all_roc_auc.xlsx
+++ b/tables/tables performance/all_roc_auc.xlsx
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7506392183227705</v>
+        <v>0.7484809591792043</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8100549653154248</v>
+        <v>0.8390170131895112</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7613004944270325</v>
+        <v>0.7683559852742645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8078972211970571</v>
+        <v>0.8279449008447881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7494040829510477</v>
+        <v>0.751079137894419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8153643856371502</v>
+        <v>0.8252002570250609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7640174953187668</v>
+        <v>0.743607067504837</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8205003113739783</v>
+        <v>0.8355889861851098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7666577017838299</v>
+        <v>0.7550117649615689</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8058392846026152</v>
+        <v>0.8263612991910682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7525631929292718</v>
+        <v>0.7698686809345732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8137869646380721</v>
+        <v>0.8310538320783639</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7488435911990055</v>
+        <v>0.7706566182637145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7942890296817697</v>
+        <v>0.8156348006878869</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7581399077861342</v>
+        <v>0.7739951221038244</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7775391281082421</v>
+        <v>0.8113412843928379</v>
       </c>
     </row>
     <row r="6">
@@ -843,221 +843,221 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>kdd_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9779664880884532</v>
+        <v>0.5217933603207073</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984734412401687</v>
+        <v>0.5269277159758483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9800866294312094</v>
+        <v>0.5276241668507725</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9807705459933888</v>
+        <v>0.5171824630326862</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9759945286675024</v>
+        <v>0.5263510976506007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9828678901174056</v>
+        <v>0.5356215274765859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9762623959876896</v>
+        <v>0.5222087186336476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9841160378433832</v>
+        <v>0.5411772963909067</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9729681978798588</v>
+        <v>0.5255292885415355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9850678217257496</v>
+        <v>0.5328166719089811</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9791576427675824</v>
+        <v>0.5287959398178579</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9832411945742618</v>
+        <v>0.5267688530069703</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9803146016186026</v>
+        <v>0.5273760243269079</v>
       </c>
       <c r="O8" t="n">
-        <v>0.981907557278012</v>
+        <v>0.5260271843351658</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9808446369542916</v>
+        <v>0.5266947229100457</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9809472244386184</v>
+        <v>0.5139647176642512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
+          <t>synth_credit_card_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9517596616208888</v>
+        <v>0.9779664880884532</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9891622918971044</v>
+        <v>0.984734412401687</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9475030501561176</v>
+        <v>0.9800866294312094</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9929164681357951</v>
+        <v>0.9807705459933888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9453801737274042</v>
+        <v>0.9759945286675024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9917156000144388</v>
+        <v>0.9828678901174056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.940992770382288</v>
+        <v>0.9762623959876896</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9913616168921412</v>
+        <v>0.9841160378433832</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9474820742092928</v>
+        <v>0.9729681978798588</v>
       </c>
       <c r="K9" t="n">
-        <v>0.988602481249146</v>
+        <v>0.9850678217257496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9581631440328582</v>
+        <v>0.9791576427675824</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9920530225680612</v>
+        <v>0.9832411945742618</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9490309263398899</v>
+        <v>0.9803146016186026</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9910818669121232</v>
+        <v>0.981907557278012</v>
       </c>
       <c r="P9" t="n">
-        <v>0.946214926427553</v>
+        <v>0.9808446369542916</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9884774905955668</v>
+        <v>0.9809472244386184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_ROC_AUC.csv</t>
+          <t>synth_mobile_money_fraud_label_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7712015433266675</v>
+        <v>0.9517596616208888</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8197175377804857</v>
+        <v>0.9891622918971044</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8166840787119661</v>
+        <v>0.9475030501561176</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5910643071460518</v>
+        <v>0.9929164681357951</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7680401578563902</v>
+        <v>0.9453801737274042</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8197977980876632</v>
+        <v>0.9917156000144388</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7955366454895971</v>
+        <v>0.940992770382288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8141940582243963</v>
+        <v>0.9913616168921412</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7795745981610667</v>
+        <v>0.9474820742092928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8254444810261332</v>
+        <v>0.988602481249146</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8164138656405653</v>
+        <v>0.9581631440328582</v>
       </c>
       <c r="M10" t="n">
-        <v>0.677596150792525</v>
+        <v>0.9920530225680612</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8160856754539733</v>
+        <v>0.9490309263398899</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6693573439727976</v>
+        <v>0.9910818669121232</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8162927427474767</v>
+        <v>0.946214926427553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6689939905739033</v>
+        <v>0.9884774905955668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ulb_credit_card_fraud_label_ROC_AUC.csv</t>
+          <t>telco_customer_churn_ROC_AUC.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9763423555732462</v>
+        <v>0.7712015433266675</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9755620027359532</v>
+        <v>0.8197175377804857</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9810699383724282</v>
+        <v>0.8166840787119661</v>
       </c>
       <c r="E11" t="n">
-        <v>0.977437823407497</v>
+        <v>0.5910643071460518</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9771127002209808</v>
+        <v>0.7680401578563902</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9822537642230672</v>
+        <v>0.8197977980876632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9742949659378416</v>
+        <v>0.7955366454895971</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9769108207401712</v>
+        <v>0.8141940582243963</v>
       </c>
       <c r="J11" t="n">
-        <v>0.974643250934479</v>
+        <v>0.7795745981610667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9777978322833312</v>
+        <v>0.8254444810261332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9783605784847944</v>
+        <v>0.8164138656405653</v>
       </c>
       <c r="M11" t="n">
-        <v>0.977037209876882</v>
+        <v>0.677596150792525</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9788180957217564</v>
+        <v>0.8160856754539733</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9816601356081091</v>
+        <v>0.6693573439727976</v>
       </c>
       <c r="P11" t="n">
-        <v>0.974538593866524</v>
+        <v>0.8162927427474767</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9795495514043492</v>
+        <v>0.6689939905739033</v>
       </c>
     </row>
     <row r="12">
